--- a/excel_config/indir/战斗表现.xlsx
+++ b/excel_config/indir/战斗表现.xlsx
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>[{"op":"tween","prop":"scale","to":{"anchor":"hit_squash"},"duration_key":"hit.squash_duration","trans_key":"hit.squash_trans","ease_key":"hit.squash_ease"},{"op":"tween","prop":"position","to":{"anchor":"knockback"},"duration_key":"hit.knockback_duration","trans_key":"hit.squash_trans","ease_key":"hit.squash_ease"},{"op":"tween","prop":"modulate","to":{"anchor":"hit_flash"},"duration_key":"hit.flash_in_duration","trans_key":"hit.squash_trans","ease_key":"hit.squash_ease"}]</t>
+          <t>[{"op": "tween", "prop": "scale", "to": {"anchor": "hit_squash"}, "duration_key": "hit.squash_duration", "trans_key": "hit.squash_trans", "ease_key": "hit.squash_ease"}, {"op": "tween", "prop": "position", "to": {"anchor": "knockback"}, "duration_key": "hit.knockback_duration", "trans_key": "hit.squash_trans", "ease_key": "hit.squash_ease"}, {"op": "tween", "prop": "modulate", "to": {"anchor": "hit_flash"}, "duration_key": "hit.flash_in_duration", "trans_key": "hit.squash_trans", "ease_key": "hit.squash_ease"}]</t>
         </is>
       </c>
       <c r="E5" s="7" t="n"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>[{"op":"tween","prop":"scale","to":{"anchor":"rest_scale"},"duration_key":"hit.recover_duration","trans_key":"hit.squash_trans","ease_key":"hit.squash_ease"},{"op":"tween","prop":"position","to":{"anchor":"rest"},"duration_key":"hit.recover_duration","trans_key":"hit.squash_trans","ease_key":"hit.squash_ease"},{"op":"tween","prop":"modulate","to":{"anchor":"rest_modulate"},"duration_key":"hit.flash_out_duration","trans_key":"hit.flash_trans","ease_key":"hit.flash_ease"}]</t>
+          <t>[{"op": "tween", "prop": "scale", "to": {"anchor": "rest_scale"}, "duration_key": "hit.recover_duration", "trans_key": "hit.squash_trans", "ease_key": "hit.squash_ease"}, {"op": "tween", "prop": "position", "to": {"anchor": "rest"}, "duration_key": "hit.recover_duration", "trans_key": "hit.squash_trans", "ease_key": "hit.squash_ease"}, {"op": "tween", "prop": "modulate", "to": {"anchor": "rest_modulate"}, "duration_key": "hit.flash_out_duration", "trans_key": "hit.flash_trans", "ease_key": "hit.flash_ease"}]</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>[{"op":"tween","prop":"position","to":{"anchor":"windup"},"duration_key":"melee.windup_duration","trans_key":"melee.windup_trans","ease_key":"melee.windup_ease"},{"op":"tween","prop":"scale","to":{"anchor":"melee_squash"},"duration_key":"melee.windup_duration","trans_key":"melee.windup_trans","ease_key":"melee.windup_ease"}]</t>
+          <t>[{"op": "tween", "prop": "position", "to": {"anchor": "windup"}, "duration_key": "melee.windup_duration", "trans_key": "melee.windup_trans", "ease_key": "melee.windup_ease"}, {"op": "tween", "prop": "scale", "to": {"anchor": "melee_squash"}, "duration_key": "melee.windup_duration", "trans_key": "melee.windup_trans", "ease_key": "melee.windup_ease"}]</t>
         </is>
       </c>
       <c r="E6" s="7" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>{"anchor":"strike"}</t>
+          <t>{"anchor": "strike"}</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2839,7 +2839,7 @@
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>[{"_comment":"施法者：恢复缩放与回静止位","op":"parallel","actor":"caster","steps":[{"op":"tween","prop":"scale","to":{"anchor":"rest_scale"},"duration":0.077,"trans_key":"melee.return_trans","ease_key":"melee.return_ease"},{"op":"tween","prop":"position","to":{"anchor":"rest"},"duration_key":"melee.return_duration","trans_key":"melee.return_trans","ease_key":"melee.return_ease"}]},{"_comment":"目标：受击反馈（hit_default）","op":"impact"}]</t>
+          <t>[{"_comment": "施法者：恢复缩放与回静止位", "op": "parallel", "actor": "caster", "steps": [{"op": "tween", "prop": "scale", "to": {"anchor": "rest_scale"}, "duration": 0.077, "trans_key": "melee.return_trans", "ease_key": "melee.return_ease"}, {"op": "tween", "prop": "position", "to": {"anchor": "rest"}, "duration_key": "melee.return_duration", "trans_key": "melee.return_trans", "ease_key": "melee.return_ease"}]}, {"_comment": "目标：受击反馈（hit_default）", "op": "impact"}]</t>
         </is>
       </c>
       <c r="E8" s="7" t="n"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>{"anchor":"recoil"}</t>
+          <t>{"anchor": "recoil"}</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -3138,7 +3138,7 @@
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>[{"op":"sequence","steps":[{"op":"tween","actor":"caster","prop":"position","to":{"anchor":"rest"},"duration_key":"ranged.settle_duration","trans_key":"ranged.settle_trans","ease_key":"ranged.settle_ease"},{"op":"resume_idle","actor":"caster"}]},{"op":"sequence","steps":[{"op":"projectile","texture":"res://assets/art/effect/image_cutout_194x82.png","visual_size":[80,34],"rotation_offset_deg":0},{"op":"impact"}]}]</t>
+          <t>[{"op": "sequence", "steps": [{"op": "tween", "actor": "caster", "prop": "position", "to": {"anchor": "rest"}, "duration_key": "ranged.settle_duration", "trans_key": "ranged.settle_trans", "ease_key": "ranged.settle_ease"}, {"op": "resume_idle", "actor": "caster"}]}, {"op": "sequence", "steps": [{"op": "projectile", "texture": "res://assets/art/effect/image_cutout_194x82.png", "visual_size": [80, 34], "rotation_offset_deg": 0}, {"op": "impact"}]}]</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>{"anchor":"recoil"}</t>
+          <t>{"anchor": "recoil"}</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>{"anchor":"release"}</t>
+          <t>{"anchor": "release"}</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -3452,7 +3452,7 @@
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>[{"_comment":"施法者回静止位","op":"sequence","steps":[{"op":"tween","actor":"caster","prop":"position","to":{"anchor":"rest"},"duration_key":"ranged.settle_duration","trans_key":"ranged.settle_trans","ease_key":"ranged.settle_ease"},{"op":"resume_idle","actor":"caster"}]},{"_comment":"弹道到达后受击","op":"sequence","steps":[{"op":"projectile"},{"op":"impact"}]}]</t>
+          <t>[{"_comment": "施法者回静止位", "op": "sequence", "steps": [{"op": "tween", "actor": "caster", "prop": "position", "to": {"anchor": "rest"}, "duration_key": "ranged.settle_duration", "trans_key": "ranged.settle_trans", "ease_key": "ranged.settle_ease"}, {"op": "resume_idle", "actor": "caster"}]}, {"_comment": "弹道到达后受击", "op": "sequence", "steps": [{"op": "projectile"}, {"op": "impact"}]}]</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>{"anchor":"recoil"}</t>
+          <t>{"anchor": "recoil"}</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>{"anchor":"release"}</t>
+          <t>{"anchor": "release"}</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -3766,7 +3766,7 @@
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>[{"op":"tween","actor":"caster","prop":"position","to":{"anchor":"rest"},"duration_key":"ranged.settle_duration","trans_key":"ranged.settle_trans","ease_key":"ranged.settle_ease"},{"op":"resume_idle","actor":"caster"}]</t>
+          <t>[{"op": "tween", "actor": "caster", "prop": "position", "to": {"anchor": "rest"}, "duration_key": "ranged.settle_duration", "trans_key": "ranged.settle_trans", "ease_key": "ranged.settle_ease"}, {"op": "resume_idle", "actor": "caster"}]</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>{"anchor":"recoil"}</t>
+          <t>{"anchor": "recoil"}</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -4037,7 +4037,7 @@
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>[{"op":"sequence","steps":[{"op":"tween","actor":"caster","prop":"position","to":{"anchor":"rest"},"duration":0.12,"trans":"quad","ease":"out"},{"op":"resume_idle","actor":"caster"}]},{"op":"sequence","steps":[{"op":"projectile","texture":"res://assets/art/effect/image_cutout_167x69.png","visual_size":[88,36],"rotation_offset_deg":0,"use_bezier":false},{"op":"impact"}]}]</t>
+          <t>[{"op": "sequence", "steps": [{"op": "tween", "actor": "caster", "prop": "position", "to": {"anchor": "rest"}, "duration": 0.12, "trans": "quad", "ease": "out"}, {"op": "resume_idle", "actor": "caster"}]}, {"op": "sequence", "steps": [{"op": "projectile", "texture": "res://assets/art/effect/image_cutout_167x69.png", "visual_size": [88, 36], "rotation_offset_deg": 0, "use_bezier": false}, {"op": "impact"}]}]</t>
         </is>
       </c>
     </row>
